--- a/Codigo Postal - Plantas.xlsx
+++ b/Codigo Postal - Plantas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\compaq\Desktop\aiudica\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364D57CF-7AAB-47B4-8801-7A53470A9393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF33B19F-1AD8-405C-A2E6-5CCD0EB037E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="372">
   <si>
     <t>PLANTA LA CALERA</t>
   </si>
@@ -1149,6 +1149,9 @@
   </si>
   <si>
     <t>PLANTA VINA DEL MAR</t>
+  </si>
+  <si>
+    <t>PLANTA CASTRO</t>
   </si>
 </sst>
 </file>
@@ -1867,7 +1870,7 @@
         <v>5700000</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>108</v>
+        <v>371</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -2032,7 +2035,7 @@
         <v>5770000</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>108</v>
+        <v>371</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -2340,7 +2343,7 @@
         <v>5740000</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>108</v>
+        <v>371</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -2395,7 +2398,7 @@
         <v>5730000</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>108</v>
+        <v>371</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -4155,7 +4158,7 @@
         <v>5760000</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>108</v>
+        <v>371</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -4221,7 +4224,7 @@
         <v>5780000</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>108</v>
+        <v>371</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -4232,7 +4235,7 @@
         <v>5790000</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>108</v>
+        <v>371</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -4243,7 +4246,7 @@
         <v>5720000</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>108</v>
+        <v>371</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -4320,7 +4323,7 @@
         <v>5750000</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>108</v>
+        <v>371</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">

--- a/Codigo Postal - Plantas.xlsx
+++ b/Codigo Postal - Plantas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\compaq\Desktop\aiudica\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF33B19F-1AD8-405C-A2E6-5CCD0EB037E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DFCF394-B7C5-4B62-AE31-9B5D738066BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="371">
   <si>
     <t>PLANTA LA CALERA</t>
   </si>
@@ -66,9 +66,6 @@
   </si>
   <si>
     <t>VITACURA</t>
-  </si>
-  <si>
-    <t>PLANTA VIÑA DEL MAR</t>
   </si>
   <si>
     <t>VINA DEL MAR</t>
@@ -1501,18 +1498,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B2" s="3">
         <v>2710000</v>
@@ -1523,7 +1520,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B3" s="3">
         <v>9650000</v>
@@ -1534,7 +1531,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B4" s="3">
         <v>4590000</v>
@@ -1545,84 +1542,84 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B5" s="3">
         <v>1650000</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B6" s="3">
         <v>1130000</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B7" s="3">
         <v>5710000</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B8" s="3">
         <v>1750000</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B9" s="3">
         <v>4650000</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B10" s="3">
         <v>6360000</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B11" s="3">
         <v>1240000</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B12" s="3">
         <v>4490000</v>
@@ -1633,40 +1630,40 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B13" s="3">
         <v>4360000</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B14" s="3">
         <v>1000000</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B15" s="3">
         <v>6000000</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B16" s="3">
         <v>9500000</v>
@@ -1677,7 +1674,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B17" s="3">
         <v>3930000</v>
@@ -1688,7 +1685,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B18" s="3">
         <v>2050000</v>
@@ -1699,18 +1696,18 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B19" s="3">
         <v>6350000</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B20" s="3">
         <v>4470000</v>
@@ -1721,40 +1718,40 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B21" s="3">
         <v>1390000</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B22" s="3">
         <v>5570000</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B23" s="3">
         <v>1570000</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B24" s="3">
         <v>2290000</v>
@@ -1765,7 +1762,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B25" s="3">
         <v>9560000</v>
@@ -1776,7 +1773,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B26" s="3">
         <v>2130000</v>
@@ -1787,29 +1784,29 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B27" s="3">
         <v>1040000</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B28" s="3">
         <v>1150000</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B29" s="3">
         <v>1960000</v>
@@ -1820,29 +1817,29 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B30" s="3">
         <v>4390000</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B31" s="3">
         <v>5010000</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B32" s="3">
         <v>2680000</v>
@@ -1853,29 +1850,29 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B33" s="3">
         <v>2480000</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B34" s="3">
         <v>5700000</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B35" s="3">
         <v>2230000</v>
@@ -1886,7 +1883,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B36" s="3">
         <v>3690000</v>
@@ -1897,7 +1894,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B37" s="3">
         <v>9200000</v>
@@ -1908,7 +1905,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B38" s="3">
         <v>9080000</v>
@@ -1919,29 +1916,29 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B39" s="3">
         <v>5850000</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B40" s="3">
         <v>1490000</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B41" s="3">
         <v>3720000</v>
@@ -1952,40 +1949,40 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B42" s="3">
         <v>3120000</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B43" s="3">
         <v>4100000</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B44" s="3">
         <v>6050000</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B45" s="3">
         <v>3780000</v>
@@ -1996,7 +1993,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B46" s="3">
         <v>3820000</v>
@@ -2007,51 +2004,51 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B47" s="3">
         <v>3090000</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B48" s="3">
         <v>5040000</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B49" s="3">
         <v>5770000</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B50" s="3">
         <v>6010000</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B51" s="3">
         <v>3990000</v>
@@ -2062,40 +2059,40 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B52" s="3">
         <v>5560000</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B53" s="3">
         <v>6100000</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B54" s="3">
         <v>2900000</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B55" s="3">
         <v>3970000</v>
@@ -2106,7 +2103,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B56" s="3">
         <v>3870000</v>
@@ -2117,18 +2114,18 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B57" s="3">
         <v>3010000</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B58" s="3">
         <v>3610000</v>
@@ -2139,18 +2136,18 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B59" s="3">
         <v>1160000</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B60" s="3">
         <v>9340000</v>
@@ -2161,51 +2158,51 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B61" s="3">
         <v>4680000</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B62" s="3">
         <v>3000000</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B63" s="3">
         <v>1890000</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B64" s="3">
         <v>4030000</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B65" s="3">
         <v>8540000</v>
@@ -2216,18 +2213,18 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B66" s="3">
         <v>2510000</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B67" s="3">
         <v>3560000</v>
@@ -2238,95 +2235,95 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B68" s="3">
         <v>4400000</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B69" s="3">
         <v>1530000</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B70" s="3">
         <v>1780000</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B71" s="3">
         <v>4190000</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B72" s="3">
         <v>5190000</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B73" s="3">
         <v>5950000</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B74" s="3">
         <v>4890000</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B75" s="3">
         <v>4700000</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B76" s="3">
         <v>9630000</v>
@@ -2337,40 +2334,40 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B77" s="3">
         <v>5740000</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B78" s="3">
         <v>4370000</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B79" s="3">
         <v>4910000</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B80" s="3">
         <v>3570000</v>
@@ -2381,7 +2378,7 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B81" s="3">
         <v>3340000</v>
@@ -2392,40 +2389,40 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B82" s="3">
         <v>5730000</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B83" s="3">
         <v>1500000</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B84" s="3">
         <v>3020000</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B85" s="3">
         <v>8010000</v>
@@ -2436,7 +2433,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B86" s="3">
         <v>3900000</v>
@@ -2447,7 +2444,7 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B87" s="3">
         <v>9810000</v>
@@ -2458,7 +2455,7 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B88" s="3">
         <v>2700000</v>
@@ -2469,7 +2466,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B89" s="3">
         <v>2690000</v>
@@ -2480,7 +2477,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B90" s="3">
         <v>3540000</v>
@@ -2491,18 +2488,18 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B91" s="3">
         <v>4710000</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B92" s="3">
         <v>9160000</v>
@@ -2513,139 +2510,139 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B93" s="3">
         <v>4170000</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B94" s="3">
         <v>4940000</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B95" s="3">
         <v>1630000</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B96" s="3">
         <v>5600000</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B97" s="3">
         <v>5620000</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B98" s="3">
         <v>5870000</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B99" s="3">
         <v>5180000</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B100" s="3">
         <v>5030000</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B101" s="3">
         <v>1080000</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B102" s="3">
         <v>4960000</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B103" s="3">
         <v>2880000</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B104" s="3">
         <v>6020000</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B105" s="3">
         <v>2310000</v>
@@ -2656,18 +2653,18 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B106" s="3">
         <v>5860000</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B107" s="3">
         <v>3400000</v>
@@ -2678,51 +2675,51 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B108" s="3">
         <v>4600000</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B109" s="3">
         <v>4180000</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B110" s="3">
         <v>1140000</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B111" s="3">
         <v>1640000</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B112" s="3">
         <v>8580000</v>
@@ -2733,7 +2730,7 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B113" s="3">
         <v>1930000</v>
@@ -2744,7 +2741,7 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B114" s="3">
         <v>8380000</v>
@@ -2755,18 +2752,18 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B115" s="3">
         <v>1100000</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B116" s="3">
         <v>9790000</v>
@@ -2777,7 +2774,7 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B117" s="3">
         <v>2770000</v>
@@ -2788,7 +2785,7 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B118" s="3">
         <v>2600000</v>
@@ -2799,7 +2796,7 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B119" s="3">
         <v>7970000</v>
@@ -2810,7 +2807,7 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B120" s="3">
         <v>2280000</v>
@@ -2821,18 +2818,18 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B121" s="3">
         <v>3250000</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B122" s="3">
         <v>8240000</v>
@@ -2843,7 +2840,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B123" s="3">
         <v>8780000</v>
@@ -2854,18 +2851,18 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B124" s="3">
         <v>1740000</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B125" s="3">
         <v>2030000</v>
@@ -2876,7 +2873,7 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B126" s="3">
         <v>8820000</v>
@@ -2887,7 +2884,7 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B127" s="3">
         <v>7850000</v>
@@ -2898,62 +2895,62 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B128" s="3">
         <v>1700000</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B129" s="3">
         <v>5220000</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B130" s="3">
         <v>5250000</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B131" s="3">
         <v>5960000</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B132" s="3">
         <v>6250000</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B133" s="3">
         <v>4560000</v>
@@ -2964,7 +2961,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B134" s="3">
         <v>9380000</v>
@@ -2975,29 +2972,29 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B135" s="3">
         <v>5160000</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B136" s="3">
         <v>3030000</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B137" s="3">
         <v>7550000</v>
@@ -3008,29 +3005,29 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B138" s="3">
         <v>4860000</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B139" s="3">
         <v>4350000</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B140" s="3">
         <v>3410000</v>
@@ -3041,18 +3038,18 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B141" s="3">
         <v>2240000</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>10</v>
+        <v>369</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B142" s="3">
         <v>3580000</v>
@@ -3063,18 +3060,18 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B143" s="3">
         <v>3240000</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B144" s="3">
         <v>2220000</v>
@@ -3085,18 +3082,18 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B145" s="3">
         <v>5610000</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B146" s="3">
         <v>7690000</v>
@@ -3107,7 +3104,7 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B147" s="3">
         <v>9120000</v>
@@ -3118,7 +3115,7 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B148" s="3">
         <v>8980000</v>
@@ -3129,29 +3126,29 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B149" s="3">
         <v>3140000</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B150" s="3">
         <v>4970000</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B151" s="3">
         <v>3620000</v>
@@ -3162,29 +3159,29 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B152" s="3">
         <v>4690000</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B153" s="3">
         <v>4380000</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B154" s="3">
         <v>2100000</v>
@@ -3195,7 +3192,7 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B155" s="3">
         <v>4430000</v>
@@ -3206,40 +3203,40 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B156" s="3">
         <v>5170000</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B157" s="3">
         <v>5590000</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B158" s="3">
         <v>4760000</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B159" s="3">
         <v>1940000</v>
@@ -3250,40 +3247,40 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B160" s="3">
         <v>4210000</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B161" s="3">
         <v>4740000</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B162" s="3">
         <v>2910000</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B163" s="3">
         <v>7810000</v>
@@ -3294,18 +3291,18 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B164" s="3">
         <v>5200000</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B165" s="3">
         <v>9250000</v>
@@ -3316,40 +3313,40 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B166" s="3">
         <v>2950000</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B167" s="3">
         <v>3260000</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B168" s="3">
         <v>1360000</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B169" s="3">
         <v>9620000</v>
@@ -3360,18 +3357,18 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B170" s="3">
         <v>5150000</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B171" s="3">
         <v>3530000</v>
@@ -3382,40 +3379,40 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B172" s="3">
         <v>5580000</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B173" s="3">
         <v>1310000</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B174" s="3">
         <v>4900000</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B175" s="3">
         <v>9580000</v>
@@ -3426,7 +3423,7 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B176" s="3">
         <v>3380000</v>
@@ -3437,29 +3434,29 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B177" s="3">
         <v>1880000</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B178" s="3">
         <v>2890000</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B179" s="3">
         <v>4530000</v>
@@ -3470,7 +3467,7 @@
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B180" s="3">
         <v>4550000</v>
@@ -3481,40 +3478,40 @@
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B181" s="3">
         <v>3110000</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B182" s="3">
         <v>6160000</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B183" s="3">
         <v>3230000</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B184" s="3">
         <v>4540000</v>
@@ -3525,7 +3522,7 @@
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B185" s="3">
         <v>4010000</v>
@@ -3536,7 +3533,7 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B186" s="3">
         <v>3850000</v>
@@ -3547,7 +3544,7 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B187" s="3">
         <v>2300000</v>
@@ -3558,18 +3555,18 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B188" s="3">
         <v>5020000</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B189" s="3">
         <v>7750000</v>
@@ -3580,73 +3577,73 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B190" s="3">
         <v>6110000</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B191" s="3">
         <v>2920000</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B192" s="3">
         <v>1420000</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B193" s="3">
         <v>2330000</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>10</v>
+        <v>369</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B194" s="3">
         <v>5290000</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B195" s="3">
         <v>1840000</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B196" s="3">
         <v>9710000</v>
@@ -3657,40 +3654,40 @@
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B197" s="3">
         <v>4850000</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B198" s="3">
         <v>1770000</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B199" s="3">
         <v>5230000</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B200" s="3">
         <v>9540000</v>
@@ -3701,40 +3698,40 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B201" s="3">
         <v>5880000</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B202" s="3">
         <v>3160000</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B203" s="3">
         <v>5210000</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B204" s="3">
         <v>2210000</v>
@@ -3745,7 +3742,7 @@
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B205" s="3">
         <v>2070000</v>
@@ -3756,18 +3753,18 @@
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B206" s="3">
         <v>3270000</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B207" s="3">
         <v>3630000</v>
@@ -3778,7 +3775,7 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B208" s="3">
         <v>8460000</v>
@@ -3789,7 +3786,7 @@
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B209" s="3">
         <v>3500000</v>
@@ -3800,7 +3797,7 @@
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B210" s="3">
         <v>3710000</v>
@@ -3811,7 +3808,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B211" s="3">
         <v>3910000</v>
@@ -3822,7 +3819,7 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B212" s="3">
         <v>9750000</v>
@@ -3833,7 +3830,7 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B213" s="3">
         <v>7910000</v>
@@ -3844,7 +3841,7 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B214" s="3">
         <v>3550000</v>
@@ -3855,40 +3852,40 @@
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B215" s="3">
         <v>4140000</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B216" s="3">
         <v>3170000</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B217" s="3">
         <v>4870000</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B218" s="3">
         <v>2040000</v>
@@ -3899,51 +3896,51 @@
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B219" s="3">
         <v>2990000</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B220" s="3">
         <v>1170000</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B221" s="3">
         <v>2980000</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B222" s="3">
         <v>3220000</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B223" s="3">
         <v>3880000</v>
@@ -3954,7 +3951,7 @@
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B224" s="3">
         <v>9480000</v>
@@ -3965,29 +3962,29 @@
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B225" s="3">
         <v>4950000</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B226" s="3">
         <v>3100000</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B227" s="3">
         <v>3960000</v>
@@ -3998,40 +3995,40 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B228" s="3">
         <v>6300000</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B229" s="3">
         <v>1180000</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B230" s="3">
         <v>6310000</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B231" s="3">
         <v>7500000</v>
@@ -4042,29 +4039,29 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B232" s="3">
         <v>2500000</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B233" s="3">
         <v>4920000</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B234" s="3">
         <v>9020000</v>
@@ -4075,7 +4072,7 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B235" s="3">
         <v>8150000</v>
@@ -4086,106 +4083,106 @@
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B236" s="3">
         <v>5500000</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B237" s="3">
         <v>5370000</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B238" s="3">
         <v>5550000</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B239" s="3">
         <v>3150000</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B240" s="3">
         <v>1900000</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B241" s="3">
         <v>6200000</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B242" s="3">
         <v>5760000</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B243" s="3">
         <v>4750000</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B244" s="3">
         <v>5380000</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B245" s="3">
         <v>2190000</v>
@@ -4196,62 +4193,62 @@
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B246" s="3">
         <v>1070000</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B247" s="3">
         <v>5360000</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B248" s="3">
         <v>5780000</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B249" s="3">
         <v>5790000</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B250" s="3">
         <v>5720000</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B251" s="3">
         <v>4520000</v>
@@ -4262,7 +4259,7 @@
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B252" s="3">
         <v>8700000</v>
@@ -4273,7 +4270,7 @@
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B253" s="3">
         <v>4500000</v>
@@ -4284,7 +4281,7 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B254" s="3">
         <v>3940000</v>
@@ -4295,7 +4292,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B255" s="3">
         <v>2260000</v>
@@ -4306,40 +4303,40 @@
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B256" s="3">
         <v>2420000</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>10</v>
+        <v>369</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B257" s="3">
         <v>5750000</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B258" s="3">
         <v>2960000</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B259" s="3">
         <v>8500000</v>
@@ -4350,18 +4347,18 @@
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B260" s="3">
         <v>2490000</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>10</v>
+        <v>369</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B261" s="3">
         <v>4000000</v>
@@ -4372,18 +4369,18 @@
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B262" s="3">
         <v>2820000</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B263" s="3">
         <v>3950000</v>
@@ -4394,7 +4391,7 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B264" s="3">
         <v>3430000</v>
@@ -4405,7 +4402,7 @@
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B265" s="3">
         <v>8420000</v>
@@ -4416,18 +4413,18 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B266" s="3">
         <v>4670000</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B267" s="3">
         <v>8640000</v>
@@ -4438,29 +4435,29 @@
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B268" s="3">
         <v>2940000</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B269" s="3">
         <v>2930000</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B270" s="3">
         <v>3640000</v>
@@ -4471,7 +4468,7 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B271" s="3">
         <v>2140000</v>
@@ -4482,18 +4479,18 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B272" s="3">
         <v>5240000</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B273" s="3">
         <v>3510000</v>
@@ -4504,51 +4501,51 @@
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B274" s="3">
         <v>1870000</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B275" s="3">
         <v>6060000</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B276" s="3">
         <v>5390000</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B277" s="3">
         <v>6240000</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B278" s="3">
         <v>3370000</v>
@@ -4559,18 +4556,18 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B279" s="3">
         <v>5000000</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B280" s="3">
         <v>3390000</v>
@@ -4581,7 +4578,7 @@
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B281" s="3">
         <v>1950000</v>
@@ -4592,7 +4589,7 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B282" s="3">
         <v>2660000</v>
@@ -4603,7 +4600,7 @@
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B283" s="3">
         <v>8050000</v>
@@ -4614,7 +4611,7 @@
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B284" s="3">
         <v>3840000</v>
@@ -4625,7 +4622,7 @@
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B285" s="3">
         <v>3520000</v>
@@ -4636,7 +4633,7 @@
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B286" s="3">
         <v>2120000</v>
@@ -4647,7 +4644,7 @@
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B287" s="3">
         <v>3860000</v>
@@ -4658,7 +4655,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B288" s="3">
         <v>2170000</v>
@@ -4669,29 +4666,29 @@
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B289" s="3">
         <v>3070000</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B290" s="3">
         <v>6260000</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B291" s="3">
         <v>3890000</v>
@@ -4702,7 +4699,7 @@
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B292" s="3">
         <v>3660000</v>
@@ -4713,7 +4710,7 @@
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B293" s="3">
         <v>8940000</v>
@@ -4724,7 +4721,7 @@
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B294" s="3">
         <v>9460000</v>
@@ -4735,18 +4732,18 @@
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B295" s="3">
         <v>5400000</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B296" s="3">
         <v>8900000</v>
@@ -4757,7 +4754,7 @@
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B297" s="3">
         <v>4020000</v>
@@ -4768,18 +4765,18 @@
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B298" s="3">
         <v>5350000</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B299" s="3">
         <v>9660000</v>
@@ -4790,29 +4787,29 @@
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B300" s="3">
         <v>1410000</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B301" s="3">
         <v>4120000</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B302" s="3">
         <v>3490000</v>
@@ -4823,7 +4820,7 @@
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B303" s="3">
         <v>8860000</v>
@@ -4834,7 +4831,7 @@
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B304" s="3">
         <v>4570000</v>
@@ -4845,18 +4842,18 @@
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B305" s="3">
         <v>2970000</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B306" s="3">
         <v>4510000</v>
@@ -4867,29 +4864,29 @@
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B307" s="3">
         <v>3130000</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B308" s="3">
         <v>4230000</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B309" s="3">
         <v>2200000</v>
@@ -4900,7 +4897,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B310" s="3">
         <v>8320000</v>
@@ -4911,7 +4908,7 @@
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B311" s="3">
         <v>2720000</v>
@@ -4922,18 +4919,18 @@
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B312" s="3">
         <v>1320000</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B313" s="3">
         <v>9670000</v>
@@ -4944,7 +4941,7 @@
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B314" s="3">
         <v>3460000</v>
@@ -4955,40 +4952,40 @@
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B315" s="3">
         <v>4260000</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B316" s="3">
         <v>1300000</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B317" s="3">
         <v>4780000</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B318" s="3">
         <v>3360000</v>
@@ -4999,29 +4996,29 @@
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B319" s="3">
         <v>4990000</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B320" s="3">
         <v>1580000</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B321" s="3">
         <v>9420000</v>
@@ -5032,95 +5029,95 @@
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B322" s="3">
         <v>6320000</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B323" s="3">
         <v>4410000</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B324" s="3">
         <v>1340000</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B325" s="3">
         <v>4980000</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B326" s="3">
         <v>4160000</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B327" s="3">
         <v>6170000</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B328" s="3">
         <v>6120000</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B329" s="3">
         <v>4730000</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B330" s="3">
         <v>3980000</v>
@@ -5131,7 +5128,7 @@
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B331" s="3">
         <v>4480000</v>
@@ -5142,40 +5139,40 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B332" s="3">
         <v>5090000</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B333" s="3">
         <v>1610000</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B334" s="3">
         <v>2340000</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B335" s="3">
         <v>3420000</v>
@@ -5186,40 +5183,40 @@
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B336" s="3">
         <v>4720000</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B337" s="3">
         <v>1760000</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B338" s="3">
         <v>4880000</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B339" s="3">
         <v>3650000</v>
@@ -5230,35 +5227,35 @@
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B340" s="3">
         <v>2450000</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B341" s="3">
         <v>4930000</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B342" s="3">
         <v>2520000</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
